--- a/config/dialogue.xlsx
+++ b/config/dialogue.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.83203125" customWidth="1" min="1" max="1"/>
@@ -1035,6 +1035,541 @@
           <t>靠近石钵，按 E 确认那道倒影。看完就走——天黑之前，我们还有一场架要打。</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>c1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>corridor_act</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>enter</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>凛音</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>vermilion_500</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/rinne_half.png</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>第二夜。回廊的灯比昨夜低了三寸——雾在往屋里走。</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>c2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>corridor_act</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>hakuyo</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>薄荷</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>fuji_500</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/hakuyo_half.png</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>钟就在头上。没有风，注连绳却是湿的……像被谁的眼泪泡过。</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>night3_procession</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>enter</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>hakuyo</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>薄荷</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>fuji_500</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/hakuyo_half.png</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>凛音，你听。纸在响——好多好多张纸，在夜里摩擦的声音。</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>night3_procession</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>凛音</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>vermilion_500</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/rinne_half.png</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>列队。纸人形抬着一口空棺，正沿着回廊往本殿去。……棺是空的，重量却在。</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>night3_procession</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>sayo</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>？？？</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>paper_300</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>（棺中传来三声轻叩。不快，不慢，像在数谁的脚步。）</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>m1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>night4_mirror</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>enter</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>凛音</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>vermilion_500</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/rinne_half.png</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>第四夜。棺停在御神木下了。树洞里那圈纹路，和棺盖上的一模一样。</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>night4_mirror</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>hakuyo</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>薄荷</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>fuji_500</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/hakuyo_half.png</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>棺里没有尸气，凛音……棺底嵌着一面镜子。镜中的人，穿着七十年前的嫁衣。</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>night4_mirror</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>凛音</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>vermilion_500</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/rinne_half.png</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>不是怨灵。四夜的异象，从头到尾，只是一个人想被好好送走。</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>hd1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>honden_act</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>enter</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>hakuyo</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>薄荷</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>fuji_500</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/hakuyo_half.png</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>逢魔刻。纸人形都在本殿前列队了——它们在等一个仪式开始。</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>hd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>hd2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>honden_act</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>凛音</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>vermilion_500</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/rinne_half.png</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>也是结束。它催人三夜，叩门三声。今晚，换我叩门。</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>hd3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>honden_act</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>guanshou</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>棺守</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ink_700</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>来者——是送行的，还是夺棺的？</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/dialogue.xlsx
+++ b/config/dialogue.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.83203125" customWidth="1" min="1" max="1"/>
@@ -1039,20 +1039,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>r1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>corridor_act</t>
+          <t>test_approach</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>enter</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>rinne</t>
@@ -1080,24 +1084,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>第二夜。回廊的灯比昨夜低了三寸——雾在往屋里走。</t>
+          <t>这条石阶……祖母讲过。她说小时候从山上下来，就是踩着这些台阶，一手牵着她娘，一手拎着那盏没送出去的灯。</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>r2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>r2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>corridor_act</t>
+          <t>test_approach</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1129,76 +1133,76 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>钟就在头上。没有风，注连绳却是湿的……像被谁的眼泪泡过。</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>没送出去的灯？……委托单上写的是「查明异象的来路」——你从看到地名的那一刻起，就知道来路了吧。</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>r3</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>r3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>night3_procession</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>enter</t>
-        </is>
-      </c>
+          <t>test_approach</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>hakuyo</t>
+          <t>rinne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>薄荷</t>
+          <t>凛音</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>fuji_500</t>
+          <t>vermilion_500</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>res://assets/chars/portraits/hakuyo_half.png</t>
+          <t>res://assets/chars/portraits/rinne_half.png</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>凛音，你听。纸在响——好多好多张纸，在夜里摩擦的声音。</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
+          <t>嗯。所以才接。「退魔寮乙字科，凛音——接下逢魔神社的夜巡。」这句话，我练了十年。</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>night3_procession</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>corridor_act</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>enter</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
@@ -1227,48 +1231,48 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>列队。纸人形抬着一口空棺，正沿着回廊往本殿去。……棺是空的，重量却在。</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>第二夜。回廊的灯比昨夜低了三寸——雾在往屋里走。</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>c2</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>night3_procession</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>hotspot</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
+          <t>corridor_act</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>sayo</t>
+          <t>hakuyo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>？？？</t>
+          <t>薄荷</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>paper_300</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>fuji_500</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/hakuyo_half.png</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>right</t>
@@ -1276,300 +1280,1080 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>（棺中传来三声轻叩。不快，不慢，像在数谁的脚步。）</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>钟就在头上。没有风，注连绳却是湿的……像被谁的眼泪泡过。</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>c3</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>night4_mirror</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>enter</t>
-        </is>
-      </c>
+          <t>corridor_act</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>rinne</t>
+          <t>hakuyo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>凛音</t>
+          <t>薄荷</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>vermilion_500</t>
+          <t>fuji_500</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>res://assets/chars/portraits/rinne_half.png</t>
+          <t>res://assets/chars/portraits/hakuyo_half.png</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>第四夜。棺停在御神木下了。树洞里那圈纹路，和棺盖上的一模一样。</t>
+          <t>我看过了，这口吊钟是旧式送钟——不是报时用的，是给人「送行」的。鸣三响，起灵；鸣九响，下葬。</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>c4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>night4_mirror</t>
+          <t>corridor_act</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>hakuyo</t>
+          <t>rinne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>薄荷</t>
+          <t>凛音</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>fuji_500</t>
+          <t>vermilion_500</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>res://assets/chars/portraits/hakuyo_half.png</t>
+          <t>res://assets/chars/portraits/rinne_half.png</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>棺里没有尸气，凛音……棺底嵌着一面镜子。镜中的人，穿着七十年前的嫁衣。</t>
+          <t>它昨夜鸣了几响？</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>night4_mirror</t>
+          <t>corridor_act</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>rinne</t>
+          <t>hakuyo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>凛音</t>
+          <t>薄荷</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>vermilion_500</t>
+          <t>fuji_500</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>res://assets/chars/portraits/rinne_half.png</t>
+          <t>res://assets/chars/portraits/hakuyo_half.png</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>不是怨灵。四夜的异象，从头到尾，只是一个人想被好好送走。</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>……三响。凛音，这口钟不是在报时，是在起灵。有人在这座神社里，办了一场没人看见的葬礼——办了七十年。</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>c6</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hd1</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>honden_act</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>enter</t>
-        </is>
-      </c>
+          <t>corridor_act</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>hakuyo</t>
+          <t>rinne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>薄荷</t>
+          <t>凛音</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>fuji_500</t>
+          <t>vermilion_500</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>res://assets/chars/portraits/hakuyo_half.png</t>
+          <t>res://assets/chars/portraits/rinne_half.png</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>逢魔刻。纸人形都在本殿前列队了——它们在等一个仪式开始。</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>hd2</t>
-        </is>
-      </c>
+          <t>那就让它办完。</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hd2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>honden_act</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>night3_procession</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>enter</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>rinne</t>
+          <t>hakuyo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>凛音</t>
+          <t>薄荷</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>vermilion_500</t>
+          <t>fuji_500</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>res://assets/chars/portraits/rinne_half.png</t>
+          <t>res://assets/chars/portraits/hakuyo_half.png</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>也是结束。它催人三夜，叩门三声。今晚，换我叩门。</t>
+          <t>凛音，你听。纸在响——好多好多张纸，在夜里摩擦的声音。</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>h3</t>
+          <t>p2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hd3</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>honden_act</t>
+          <t>night3_procession</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>凛音</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>vermilion_500</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/rinne_half.png</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>列队。纸人形抬着一口空棺，正沿着回廊往本殿去。……棺是空的，重量却在。</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>night3_procession</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>sayo</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>？？？</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>paper_300</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>（棺中传来三声轻叩。不快，不慢，像在数谁的脚步。）</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>night3_procession</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>hakuyo</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>薄荷</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>fuji_500</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/hakuyo_half.png</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>书上写过这种列队——扎纸守灵。人走了，心里的念头没走，就会附在守灵的纸人身上，一遍一遍，继续做生前没做完的那件事。</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>night3_procession</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>凛音</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>vermilion_500</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/rinne_half.png</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>它们抬了七十年。抬棺的人不累——因为走路的早就不是人了。累的是那个下命令的。</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>night3_procession</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>hakuyo</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>薄荷</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>fuji_500</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/hakuyo_half.png</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>凛音，我在数——每圈列队经过，棺里都叩三下。她在催人。可她催的不是我们……是让她等的那个人。</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>m1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>night4_mirror</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>enter</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>凛音</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>vermilion_500</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/rinne_half.png</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>第四夜。棺停在御神木下了。树洞里那圈纹路，和棺盖上的一模一样。</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>night4_mirror</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>hakuyo</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>薄荷</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>fuji_500</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/hakuyo_half.png</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>棺里没有尸气，凛音……棺底嵌着一面镜子。镜中的人，穿着七十年前的嫁衣。</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>night4_mirror</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>凛音</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>vermilion_500</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/rinne_half.png</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>不是怨灵。四夜的异象，从头到尾，只是一个人想被好好送走。</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>m4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>m4</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>night4_mirror</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>hakuyo</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>薄荷</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>fuji_500</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/hakuyo_half.png</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>我能听见她。很轻，像隔着很深的水……她说她叫小夜。她说等的人一直没来，问我们是不是「山下顾家派来的」。</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>m5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>m5</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>night4_mirror</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>凛音</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>vermilion_500</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/rinne_half.png</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>（沉默了一会儿）顾家。……我祖母的娘家，就姓顾。当年订下这门亲事的，是小夜的兄长。战乱起的那年，顾家整族南迁——那盏聘礼之灯，没来得及送上山。</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>m6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>m6</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>night4_mirror</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>hakuyo</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>薄荷</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>fuji_500</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/hakuyo_half.png</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>所以送葬的仪式差了最后一环，乡俗里她就进不了祖坟……七十年，就卡在这一盏灯上？</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>m7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>m7</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>night4_mirror</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>凛音</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>vermilion_500</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/rinne_half.png</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>卡在「没人记得」上。灯、钟、棺、镜——她把路标一个一个点亮了。明天是逢魔刻。该有人把这盏灯，送到她面前了。</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>hd1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>honden_act</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>enter</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>hakuyo</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>薄荷</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>fuji_500</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/hakuyo_half.png</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>逢魔刻。纸人形都在本殿前列队了——它们在等一个仪式开始。</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>hd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>hd2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>honden_act</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>凛音</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>vermilion_500</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/rinne_half.png</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>也是结束。它催人三夜，叩门三声。今晚，换我叩门。</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>hd3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>hd3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>honden_act</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>guanshou</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>棺守</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>ink_700</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>来者——是送行的，还是夺棺的？</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>hd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>hd4</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>honden_act</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>凛音</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>vermilion_500</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>res://assets/chars/portraits/rinne_half.png</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>送行的。退魔寮乙字科，凛音——受山下顾家之托，送顾氏未过门的媳妇，小夜姑娘，上路。</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>hd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>hd5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>honden_act</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>guanshou</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>棺守</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ink_700</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>……顾。七十年了。原来山下还有人，记得这个姓。（他让开了半步）……那么，拜托了。</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
